--- a/tableau_synthese_corrige.xlsx
+++ b/tableau_synthese_corrige.xlsx
@@ -118,7 +118,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -641,6 +641,34 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
@@ -1224,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col width="70.42578125" customWidth="1" style="1" min="1" max="1"/>
@@ -1741,80 +1769,7 @@
       <c r="H21" s="55" t="n"/>
     </row>
     <row r="22" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A22" s="63" t="inlineStr">
-        <is>
-          <t>Fondation.io - Landing Page (site vitrine)
-Technos : HTML, CSS
-Docs : Dépôt GitHub Fondation-io/landing-page</t>
-        </is>
-      </c>
-      <c r="B22" s="63" t="inlineStr">
-        <is>
-          <t>01/09/25 au 31/10/25</t>
-        </is>
-      </c>
-      <c r="C22" s="64" t="n"/>
-      <c r="D22" s="65" t="n"/>
-      <c r="E22" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F22" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G22" s="65" t="n"/>
-      <c r="H22" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A23" s="63" t="inlineStr">
-        <is>
-          <t>Fondation.io - fast-db-batch-search-client
-Client TypeScript pour API de recherche batch (fuzzy search, jointures, CI/CD)
-Technos : TypeScript, Node.js, API REST, GitHub Actions
-Docs : Dépôt GitHub Fondation-io/fast-db-batch-search-client | npm @fondation-io/fast-db-batch-search-client</t>
-        </is>
-      </c>
-      <c r="B23" s="63" t="inlineStr">
-        <is>
-          <t>01/11/25 au 31/01/26</t>
-        </is>
-      </c>
-      <c r="C23" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D23" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E23" s="66" t="n"/>
-      <c r="F23" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G23" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H23" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A24" s="72" t="inlineStr">
+      <c r="A22" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - Comparateur d'IA Automatisé (Testing_Claude_code)
 Framework de benchmark de LLMs en parallèle, export JSON/CSV
@@ -1822,32 +1777,108 @@
 Docs : Dépôt privé entreprise</t>
         </is>
       </c>
-      <c r="B24" s="73" t="inlineStr">
+      <c r="B22" s="73" t="inlineStr">
         <is>
           <t>01/02/25 au 30/04/25</t>
         </is>
       </c>
-      <c r="C24" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C22" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G22" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="39.95" customFormat="1" customHeight="1" s="2">
+      <c r="A23" s="72" t="inlineStr">
+        <is>
+          <t>Fondation.io - Scanner de Flux RSS Intelligent (RSSScanner)
+Veille tech automatisée multi-sources, parseur OPML, déduplication
+Technos : Python, RSS, Data Parsing, Backend
+Docs : Dépôt privé entreprise</t>
+        </is>
+      </c>
+      <c r="B23" s="73" t="inlineStr">
+        <is>
+          <t>01/06/25 au 31/08/25</t>
+        </is>
+      </c>
+      <c r="C23" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="75" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="70" customFormat="1" customHeight="1" s="2">
+      <c r="A24" s="72" t="n"/>
+      <c r="B24" s="73" t="n"/>
+      <c r="C24" s="74" t="n"/>
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="21" t="n"/>
-      <c r="F24" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G24" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F24" s="74" t="n"/>
+      <c r="G24" s="74" t="n"/>
       <c r="H24" s="22" t="n"/>
     </row>
     <row r="25" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A25" s="72" t="inlineStr">
+      <c r="A25" s="72" t="n"/>
+      <c r="B25" s="73" t="n"/>
+      <c r="C25" s="74" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="75" t="n"/>
+    </row>
+    <row r="26" ht="70" customFormat="1" customHeight="1" s="2">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="54" t="n"/>
+      <c r="C26" s="54" t="n"/>
+      <c r="D26" s="54" t="n"/>
+      <c r="E26" s="54" t="n"/>
+      <c r="F26" s="54" t="n"/>
+      <c r="G26" s="54" t="n"/>
+      <c r="H26" s="55" t="n"/>
+    </row>
+    <row r="27" ht="18" customFormat="1" customHeight="1" s="2">
+      <c r="A27" s="13" t="n"/>
+    </row>
+    <row r="28" ht="39.95" customFormat="1" customHeight="1" s="2">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Réalisations en milieu professionnel en cours de seconde année</t>
+        </is>
+      </c>
+      <c r="B28" s="54" t="n"/>
+      <c r="C28" s="54" t="n"/>
+      <c r="D28" s="54" t="n"/>
+      <c r="E28" s="54" t="n"/>
+      <c r="F28" s="54" t="n"/>
+      <c r="G28" s="54" t="n"/>
+      <c r="H28" s="55" t="n"/>
+    </row>
+    <row r="29" ht="30" customFormat="1" customHeight="1" s="2">
+      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - AgentSea
 Agents IA autonomes navigant sur le web (headless browsers, LLM-piloté)
@@ -1855,129 +1886,39 @@
 Docs : Dépôt privé entreprise</t>
         </is>
       </c>
-      <c r="B25" s="73" t="inlineStr">
+      <c r="B29" s="73" t="inlineStr">
         <is>
           <t>01/05/25 au 31/07/25</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n"/>
-      <c r="D25" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G25" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="n"/>
-    </row>
-    <row r="26" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A26" s="72" t="inlineStr">
-        <is>
-          <t>Fondation.io - Scanner de Flux RSS Intelligent (RSSScanner)
-Veille tech automatisée multi-sources, parseur OPML, déduplication
-Technos : Python, RSS, Data Parsing, Backend
-Docs : Dépôt privé entreprise</t>
-        </is>
-      </c>
-      <c r="B26" s="73" t="inlineStr">
-        <is>
-          <t>01/06/25 au 31/08/25</t>
-        </is>
-      </c>
-      <c r="C26" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="75" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A27" s="13" t="n"/>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="54" t="n"/>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-      <c r="H27" s="55" t="n"/>
-    </row>
-    <row r="28" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A28" s="13" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="21" t="n"/>
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="22" t="n"/>
-    </row>
-    <row r="29" ht="30" customFormat="1" customHeight="1" s="2">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>Réalisations en milieu professionnel en cours de seconde année</t>
-        </is>
-      </c>
-      <c r="B29" s="54" t="n"/>
-      <c r="C29" s="54" t="n"/>
-      <c r="D29" s="54" t="n"/>
-      <c r="E29" s="54" t="n"/>
-      <c r="F29" s="54" t="n"/>
-      <c r="G29" s="54" t="n"/>
-      <c r="H29" s="55" t="n"/>
-    </row>
-    <row r="30" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A30" s="63" t="inlineStr">
-        <is>
-          <t>Fondation.io - Codex (fork openai/codex)
-Agent de code IA s'exécutant en terminal (contribution open source)
-Technos : Rust, IA générative, CLI
-Docs : Dépôt GitHub Fondation-io/codex</t>
-        </is>
-      </c>
-      <c r="B30" s="63" t="inlineStr">
-        <is>
-          <t>01/02/26 au 31/03/26</t>
-        </is>
-      </c>
-      <c r="C30" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D30" s="65" t="n"/>
-      <c r="E30" s="66" t="n"/>
-      <c r="F30" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G30" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H30" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G29" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="70" customFormat="1" customHeight="1" s="2">
+      <c r="A30" s="72" t="n"/>
+      <c r="B30" s="73" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="74" t="n"/>
+      <c r="G30" s="74" t="n"/>
+      <c r="H30" s="22" t="n"/>
     </row>
     <row r="31" ht="39.95" customFormat="1" customHeight="1" s="2">
       <c r="A31" s="13" t="n"/>
@@ -2020,48 +1961,38 @@
       <c r="H34" s="22" t="n"/>
     </row>
     <row r="35" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A35" s="13" t="n"/>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="F35" s="21" t="n"/>
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="22" t="n"/>
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
+      <c r="H35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="24" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>

--- a/tableau_synthese_corrige.xlsx
+++ b/tableau_synthese_corrige.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
@@ -109,6 +109,7 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font/>
   </fonts>
   <fills count="2">
     <fill>
@@ -118,7 +119,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="47">
     <border>
       <left/>
       <right/>
@@ -670,12 +671,13 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -884,6 +886,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1465,7 +1468,7 @@
       <c r="G9" s="49" t="n"/>
       <c r="H9" s="50" t="n"/>
     </row>
-    <row r="10" ht="70" customFormat="1" customHeight="1" s="2">
+    <row r="10" ht="95" customFormat="1" customHeight="1" s="2">
       <c r="A10" s="63" t="inlineStr">
         <is>
           <t>Portfolio BTS SIO (Site web)
@@ -1478,22 +1481,22 @@
           <t>01/09/24 au 30/04/25</t>
         </is>
       </c>
-      <c r="C10" s="64" t="inlineStr"/>
-      <c r="D10" s="65" t="inlineStr"/>
+      <c r="C10" s="64" t="n"/>
+      <c r="D10" s="65" t="n"/>
       <c r="E10" s="69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" s="65" t="inlineStr"/>
-      <c r="G10" s="65" t="inlineStr"/>
+      <c r="F10" s="65" t="n"/>
+      <c r="G10" s="65" t="n"/>
       <c r="H10" s="69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customFormat="1" customHeight="1" s="2">
+    <row r="11" ht="95" customFormat="1" customHeight="1" s="2">
       <c r="A11" s="63" t="inlineStr">
         <is>
           <t>Dungeon Beast - Jeu 2D (Nuit du Code 2024, Lycée Louis Bascan)
@@ -1506,79 +1509,23 @@
           <t>01/10/24 au 31/10/24</t>
         </is>
       </c>
-      <c r="C11" s="65" t="inlineStr"/>
-      <c r="D11" s="65" t="inlineStr"/>
-      <c r="E11" s="65" t="inlineStr"/>
+      <c r="C11" s="65" t="n"/>
+      <c r="D11" s="65" t="n"/>
+      <c r="E11" s="65" t="n"/>
       <c r="F11" s="69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G11" s="65" t="inlineStr"/>
+      <c r="G11" s="65" t="n"/>
       <c r="H11" s="69" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customFormat="1" customHeight="1" s="2">
+    <row r="12" ht="115" customFormat="1" customHeight="1" s="2">
       <c r="A12" s="63" t="inlineStr">
-        <is>
-          <t>Auto-fish-bot - Bot de pêche automatique
-Technos : Python, automatisation
-Docs : Dépôt GitHub MathieuGal/Auto-fish-bot</t>
-        </is>
-      </c>
-      <c r="B12" s="63" t="inlineStr">
-        <is>
-          <t>01/11/24 au 31/12/24</t>
-        </is>
-      </c>
-      <c r="C12" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D12" s="65" t="n"/>
-      <c r="E12" s="65" t="n"/>
-      <c r="F12" s="65" t="n"/>
-      <c r="G12" s="66" t="n"/>
-      <c r="H12" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A13" s="63" t="inlineStr">
-        <is>
-          <t>Auto-bot-vote - Bot automatique de vote (Vanadia)
-Technos : Python, Playwright, Schedule, AsyncIO
-Docs : Dépôt GitHub MathieuGal/Auto-bot-vote</t>
-        </is>
-      </c>
-      <c r="B13" s="63" t="inlineStr">
-        <is>
-          <t>06/01/25 au 28/02/25</t>
-        </is>
-      </c>
-      <c r="C13" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D13" s="65" t="n"/>
-      <c r="E13" s="65" t="n"/>
-      <c r="F13" s="65" t="n"/>
-      <c r="G13" s="65" t="n"/>
-      <c r="H13" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A14" s="63" t="inlineStr">
         <is>
           <t>MCP-serveur - Serveur Model Context Protocol
 Documentation technique (LangChain, LlamaIndex, OpenAI)
@@ -1586,54 +1533,118 @@
 Docs : Dépôt GitHub MathieuGal/MCP-serveur | PulseMCP</t>
         </is>
       </c>
-      <c r="B14" s="63" t="inlineStr">
+      <c r="B12" s="63" t="inlineStr">
         <is>
           <t>03/03/25 au 30/04/25</t>
         </is>
       </c>
-      <c r="C14" s="65" t="n"/>
-      <c r="D14" s="65" t="n"/>
-      <c r="E14" s="65" t="n"/>
-      <c r="F14" s="65" t="n"/>
-      <c r="G14" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H14" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customFormat="1" customHeight="1" s="2">
-      <c r="A15" s="68" t="inlineStr">
+      <c r="C12" s="65" t="n"/>
+      <c r="D12" s="65" t="n"/>
+      <c r="E12" s="65" t="n"/>
+      <c r="F12" s="65" t="n"/>
+      <c r="G12" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H12" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customFormat="1" customHeight="1" s="2">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>── 2ème année ──</t>
         </is>
       </c>
-      <c r="B15" s="49" t="n"/>
-      <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="49" t="n"/>
-      <c r="G15" s="49" t="n"/>
-      <c r="H15" s="50" t="n"/>
-    </row>
-    <row r="16" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A16" s="70" t="inlineStr">
+      <c r="B13" s="49" t="n"/>
+      <c r="C13" s="49" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="49" t="n"/>
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="50" t="n"/>
+    </row>
+    <row r="14" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>LinkedIn Bot - Bot de publication automatique IA pour LinkedIn
 Technos : Python, Google Gemini API, Docker, RSS
 Docs : Dépôt GitHub MathieuGal/Linkedin-Manager</t>
         </is>
       </c>
+      <c r="B14" s="71" t="inlineStr">
+        <is>
+          <t>01/09/25 au 31/12/25</t>
+        </is>
+      </c>
+      <c r="C14" s="64" t="n"/>
+      <c r="D14" s="65" t="n"/>
+      <c r="E14" s="66" t="n"/>
+      <c r="F14" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G14" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>NDC Space Shooter - Jeu de tir spatial rétro (Nuit du Code 2025)
+Technos : Python, Pyxel
+Docs : Dépôt GitHub MathieuGal/NDC</t>
+        </is>
+      </c>
+      <c r="B15" s="71" t="inlineStr">
+        <is>
+          <t>01/10/25 au 30/11/25</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="n"/>
+      <c r="D15" s="65" t="n"/>
+      <c r="E15" s="66" t="n"/>
+      <c r="F15" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G15" s="65" t="n"/>
+      <c r="H15" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>Patrimonia - Application de gestion de patrimoine personnel (binôme)
+Technos : React, Vite, Tailwind CSS, Node.js, Express, SQLite, JWT, Docker
+Docs : Dépôt GitHub amory-danvy/Patrimonia</t>
+        </is>
+      </c>
       <c r="B16" s="71" t="inlineStr">
         <is>
-          <t>01/09/25 au 31/12/25</t>
-        </is>
-      </c>
-      <c r="C16" s="64" t="n"/>
+          <t>01/12/25 au 28/02/26</t>
+        </is>
+      </c>
+      <c r="C16" s="69" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D16" s="65" t="n"/>
       <c r="E16" s="66" t="n"/>
       <c r="F16" s="69" t="inlineStr">
@@ -1646,118 +1657,120 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H16" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A17" s="70" t="inlineStr">
-        <is>
-          <t>NDC Space Shooter - Jeu de tir spatial rétro (Nuit du Code 2025)
-Technos : Python, Pyxel
-Docs : Dépôt GitHub MathieuGal/NDC</t>
-        </is>
-      </c>
-      <c r="B17" s="71" t="inlineStr">
-        <is>
-          <t>01/10/25 au 30/11/25</t>
-        </is>
-      </c>
-      <c r="C17" s="64" t="n"/>
-      <c r="D17" s="65" t="n"/>
-      <c r="E17" s="66" t="n"/>
-      <c r="F17" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G17" s="65" t="n"/>
-      <c r="H17" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A18" s="70" t="inlineStr">
-        <is>
-          <t>Projet Bourse - Application de gestion et simulation boursière (binôme)
-Technos : PHP, MVC, MySQL, API REST
-Docs : Dépôt GitHub MathieuGal/Projet-Bourse</t>
-        </is>
-      </c>
-      <c r="B18" s="71" t="inlineStr">
-        <is>
-          <t>01/12/25 au 28/02/26</t>
-        </is>
-      </c>
-      <c r="C18" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D18" s="65" t="n"/>
-      <c r="E18" s="66" t="n"/>
-      <c r="F18" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G18" s="69" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H18" s="66" t="n"/>
-    </row>
-    <row r="19" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A19" s="13" t="n"/>
-      <c r="B19" s="54" t="n"/>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="54" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="54" t="n"/>
-      <c r="G19" s="54" t="n"/>
-      <c r="H19" s="55" t="n"/>
-    </row>
-    <row r="20" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A20" s="72" t="inlineStr">
+      <c r="H16" s="66" t="n"/>
+    </row>
+    <row r="17" ht="95" customFormat="1" customHeight="1" s="2">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>ArtisanConnect - Plateforme de mise en relation artisans/clients
 Technos : PHP, MySQL, CSS, Responsive
 Docs : Dépôt GitHub MathieuGal/Projet-Sites-Artisan</t>
         </is>
       </c>
+      <c r="B17" s="73" t="inlineStr">
+        <is>
+          <t>01/03/26 au 30/04/26</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G17" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="30" customFormat="1" customHeight="1" s="2">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Réalisations en milieu professionnel en cours de première année</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="54" t="n"/>
+      <c r="E18" s="54" t="n"/>
+      <c r="F18" s="54" t="n"/>
+      <c r="G18" s="54" t="n"/>
+      <c r="H18" s="55" t="n"/>
+    </row>
+    <row r="19" ht="115" customFormat="1" customHeight="1" s="2">
+      <c r="A19" s="72" t="inlineStr">
+        <is>
+          <t>Fondation.io - Comparateur d'IA Automatisé (Testing_Claude_code)
+Framework de benchmark de LLMs en parallèle, export JSON/CSV
+Technos : Python, API LLM, Automation, Data Analysis
+Docs : Dépôt privé entreprise</t>
+        </is>
+      </c>
+      <c r="B19" s="73" t="inlineStr">
+        <is>
+          <t>01/02/25 au 30/04/25</t>
+        </is>
+      </c>
+      <c r="C19" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G19" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="n"/>
+    </row>
+    <row r="20" ht="115" customFormat="1" customHeight="1" s="2">
+      <c r="A20" s="72" t="inlineStr">
+        <is>
+          <t>Fondation.io - Scanner de Flux RSS Intelligent (RSSScanner)
+Veille tech automatisée multi-sources, parseur OPML, déduplication
+Technos : Python, RSS, Data Parsing, Backend
+Docs : Dépôt privé entreprise</t>
+        </is>
+      </c>
       <c r="B20" s="73" t="inlineStr">
         <is>
-          <t>01/03/26 au 30/04/26</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>01/06/25 au 31/08/25</t>
+        </is>
+      </c>
+      <c r="C20" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="n"/>
       <c r="E20" s="21" t="n"/>
-      <c r="F20" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G20" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="n"/>
-    </row>
-    <row r="21" ht="30" customFormat="1" customHeight="1" s="2">
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="75" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39.95" customFormat="1" customHeight="1" s="2">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>Réalisations en milieu professionnel en cours de première année</t>
+          <t>Réalisations en milieu professionnel en cours de seconde année</t>
         </is>
       </c>
       <c r="B21" s="54" t="n"/>
@@ -1768,117 +1781,8 @@
       <c r="G21" s="54" t="n"/>
       <c r="H21" s="55" t="n"/>
     </row>
-    <row r="22" ht="39.95" customFormat="1" customHeight="1" s="2">
+    <row r="22" ht="115" customFormat="1" customHeight="1" s="2">
       <c r="A22" s="72" t="inlineStr">
-        <is>
-          <t>Fondation.io - Comparateur d'IA Automatisé (Testing_Claude_code)
-Framework de benchmark de LLMs en parallèle, export JSON/CSV
-Technos : Python, API LLM, Automation, Data Analysis
-Docs : Dépôt privé entreprise</t>
-        </is>
-      </c>
-      <c r="B22" s="73" t="inlineStr">
-        <is>
-          <t>01/02/25 au 30/04/25</t>
-        </is>
-      </c>
-      <c r="C22" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G22" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="n"/>
-    </row>
-    <row r="23" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A23" s="72" t="inlineStr">
-        <is>
-          <t>Fondation.io - Scanner de Flux RSS Intelligent (RSSScanner)
-Veille tech automatisée multi-sources, parseur OPML, déduplication
-Technos : Python, RSS, Data Parsing, Backend
-Docs : Dépôt privé entreprise</t>
-        </is>
-      </c>
-      <c r="B23" s="73" t="inlineStr">
-        <is>
-          <t>01/06/25 au 31/08/25</t>
-        </is>
-      </c>
-      <c r="C23" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="75" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A24" s="72" t="n"/>
-      <c r="B24" s="73" t="n"/>
-      <c r="C24" s="74" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="74" t="n"/>
-      <c r="G24" s="74" t="n"/>
-      <c r="H24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A25" s="72" t="n"/>
-      <c r="B25" s="73" t="n"/>
-      <c r="C25" s="74" t="n"/>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="75" t="n"/>
-    </row>
-    <row r="26" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A26" s="13" t="n"/>
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="54" t="n"/>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-      <c r="H26" s="55" t="n"/>
-    </row>
-    <row r="27" ht="18" customFormat="1" customHeight="1" s="2">
-      <c r="A27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>Réalisations en milieu professionnel en cours de seconde année</t>
-        </is>
-      </c>
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="54" t="n"/>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-      <c r="H28" s="55" t="n"/>
-    </row>
-    <row r="29" ht="30" customFormat="1" customHeight="1" s="2">
-      <c r="A29" s="72" t="inlineStr">
         <is>
           <t>Fondation.io - AgentSea
 Agents IA autonomes navigant sur le web (headless browsers, LLM-piloté)
@@ -1886,112 +1790,180 @@
 Docs : Dépôt privé entreprise</t>
         </is>
       </c>
-      <c r="B29" s="73" t="inlineStr">
+      <c r="B22" s="73" t="inlineStr">
         <is>
           <t>01/05/25 au 31/07/25</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="n"/>
-      <c r="F29" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G29" s="74" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H29" s="22" t="n"/>
-    </row>
-    <row r="30" ht="70" customFormat="1" customHeight="1" s="2">
-      <c r="A30" s="72" t="n"/>
-      <c r="B30" s="73" t="n"/>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="74" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="74" t="n"/>
-      <c r="G30" s="74" t="n"/>
-      <c r="H30" s="22" t="n"/>
-    </row>
-    <row r="31" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A31" s="13" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="21" t="n"/>
-      <c r="G31" s="21" t="n"/>
-      <c r="H31" s="22" t="n"/>
-    </row>
-    <row r="32" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A32" s="13" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="22" t="n"/>
-    </row>
-    <row r="33" ht="39.95" customFormat="1" customHeight="1" s="2">
-      <c r="A33" s="13" t="n"/>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="22" t="n"/>
-    </row>
-    <row r="34" ht="39.95" customFormat="1" customHeight="1" s="2" thickBot="1">
-      <c r="A34" s="13" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="22" t="n"/>
-    </row>
-    <row r="35" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A35" s="14" t="n"/>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="23" t="n"/>
-      <c r="F35" s="23" t="n"/>
-      <c r="G35" s="23" t="n"/>
-      <c r="H35" s="24" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G22" s="74" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="n"/>
+    </row>
+    <row r="23" customFormat="1" s="2">
+      <c r="A23" s="76" t="n"/>
+      <c r="B23" s="76" t="n"/>
+      <c r="C23" s="76" t="n"/>
+      <c r="D23" s="76" t="n"/>
+      <c r="E23" s="76" t="n"/>
+      <c r="F23" s="76" t="n"/>
+      <c r="G23" s="76" t="n"/>
+      <c r="H23" s="76" t="n"/>
+    </row>
+    <row r="24" customFormat="1" s="2">
+      <c r="A24" s="76" t="n"/>
+      <c r="B24" s="76" t="n"/>
+      <c r="C24" s="76" t="n"/>
+      <c r="D24" s="76" t="n"/>
+      <c r="E24" s="76" t="n"/>
+      <c r="F24" s="76" t="n"/>
+      <c r="G24" s="76" t="n"/>
+      <c r="H24" s="76" t="n"/>
+    </row>
+    <row r="25" customFormat="1" s="2">
+      <c r="A25" s="76" t="n"/>
+      <c r="B25" s="76" t="n"/>
+      <c r="C25" s="76" t="n"/>
+      <c r="D25" s="76" t="n"/>
+      <c r="E25" s="76" t="n"/>
+      <c r="F25" s="76" t="n"/>
+      <c r="G25" s="76" t="n"/>
+      <c r="H25" s="76" t="n"/>
+    </row>
+    <row r="26" customFormat="1" s="2">
+      <c r="A26" s="76" t="n"/>
+      <c r="B26" s="76" t="n"/>
+      <c r="C26" s="76" t="n"/>
+      <c r="D26" s="76" t="n"/>
+      <c r="E26" s="76" t="n"/>
+      <c r="F26" s="76" t="n"/>
+      <c r="G26" s="76" t="n"/>
+      <c r="H26" s="76" t="n"/>
+    </row>
+    <row r="27" customFormat="1" s="2">
+      <c r="A27" s="76" t="n"/>
+      <c r="B27" s="76" t="n"/>
+      <c r="C27" s="76" t="n"/>
+      <c r="D27" s="76" t="n"/>
+      <c r="E27" s="76" t="n"/>
+      <c r="F27" s="76" t="n"/>
+      <c r="G27" s="76" t="n"/>
+      <c r="H27" s="76" t="n"/>
+    </row>
+    <row r="28" customFormat="1" s="2">
+      <c r="A28" s="76" t="n"/>
+      <c r="B28" s="76" t="n"/>
+      <c r="C28" s="76" t="n"/>
+      <c r="D28" s="76" t="n"/>
+      <c r="E28" s="76" t="n"/>
+      <c r="F28" s="76" t="n"/>
+      <c r="G28" s="76" t="n"/>
+      <c r="H28" s="76" t="n"/>
+    </row>
+    <row r="29" customFormat="1" s="2">
+      <c r="A29" s="76" t="n"/>
+      <c r="B29" s="76" t="n"/>
+      <c r="C29" s="76" t="n"/>
+      <c r="D29" s="76" t="n"/>
+      <c r="E29" s="76" t="n"/>
+      <c r="F29" s="76" t="n"/>
+      <c r="G29" s="76" t="n"/>
+      <c r="H29" s="76" t="n"/>
+    </row>
+    <row r="30" customFormat="1" s="2">
+      <c r="A30" s="76" t="n"/>
+      <c r="B30" s="76" t="n"/>
+      <c r="C30" s="76" t="n"/>
+      <c r="D30" s="76" t="n"/>
+      <c r="E30" s="76" t="n"/>
+      <c r="F30" s="76" t="n"/>
+      <c r="G30" s="76" t="n"/>
+      <c r="H30" s="76" t="n"/>
+    </row>
+    <row r="31" customFormat="1" s="2">
+      <c r="A31" s="76" t="n"/>
+      <c r="B31" s="76" t="n"/>
+      <c r="C31" s="76" t="n"/>
+      <c r="D31" s="76" t="n"/>
+      <c r="E31" s="76" t="n"/>
+      <c r="F31" s="76" t="n"/>
+      <c r="G31" s="76" t="n"/>
+      <c r="H31" s="76" t="n"/>
+    </row>
+    <row r="32" customFormat="1" s="2">
+      <c r="A32" s="76" t="n"/>
+      <c r="B32" s="76" t="n"/>
+      <c r="C32" s="76" t="n"/>
+      <c r="D32" s="76" t="n"/>
+      <c r="E32" s="76" t="n"/>
+      <c r="F32" s="76" t="n"/>
+      <c r="G32" s="76" t="n"/>
+      <c r="H32" s="76" t="n"/>
+    </row>
+    <row r="33" customFormat="1" s="2">
+      <c r="A33" s="76" t="n"/>
+      <c r="B33" s="76" t="n"/>
+      <c r="C33" s="76" t="n"/>
+      <c r="D33" s="76" t="n"/>
+      <c r="E33" s="76" t="n"/>
+      <c r="F33" s="76" t="n"/>
+      <c r="G33" s="76" t="n"/>
+      <c r="H33" s="76" t="n"/>
+    </row>
+    <row r="34" customFormat="1" s="2" thickBot="1">
+      <c r="A34" s="76" t="n"/>
+      <c r="B34" s="76" t="n"/>
+      <c r="C34" s="76" t="n"/>
+      <c r="D34" s="76" t="n"/>
+      <c r="E34" s="76" t="n"/>
+      <c r="F34" s="76" t="n"/>
+      <c r="G34" s="76" t="n"/>
+      <c r="H34" s="76" t="n"/>
+    </row>
+    <row r="35" customFormat="1" s="2">
+      <c r="A35" s="76" t="n"/>
+      <c r="B35" s="76" t="n"/>
+      <c r="C35" s="76" t="n"/>
+      <c r="D35" s="76" t="n"/>
+      <c r="E35" s="76" t="n"/>
+      <c r="F35" s="76" t="n"/>
+      <c r="G35" s="76" t="n"/>
+      <c r="H35" s="76" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
+      <c r="A36" s="76" t="n"/>
+      <c r="B36" s="76" t="n"/>
+      <c r="C36" s="76" t="n"/>
+      <c r="D36" s="76" t="n"/>
+      <c r="E36" s="76" t="n"/>
+      <c r="F36" s="76" t="n"/>
+      <c r="G36" s="76" t="n"/>
+      <c r="H36" s="76" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="14">
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A15:H15"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
@@ -2000,7 +1972,7 @@
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="48"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="48" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>